--- a/analysis/experiment_analysis.xlsx
+++ b/analysis/experiment_analysis.xlsx
@@ -4614,10 +4614,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4626,7 +4623,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -83547,20 +83547,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>1447</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="16"/>
       <c r="G1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>723</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="14" t="s">
         <v>1469</v>
       </c>
-      <c r="L1" s="18"/>
+      <c r="L1" s="14"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="9" t="s">
@@ -83593,12 +83593,12 @@
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="17" t="s">
         <v>1448</v>
       </c>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickBot="1">
       <c r="A4" t="s">
@@ -83846,10 +83846,10 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.6">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="18" t="s">
         <v>1459</v>
       </c>
-      <c r="B17" s="15"/>
+      <c r="B17" s="18"/>
       <c r="G17" s="1">
         <v>0</v>
       </c>
@@ -83866,10 +83866,10 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="15" t="s">
         <v>1460</v>
       </c>
-      <c r="B19" s="16"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="7">
         <v>3.1899999999999998E-2</v>
       </c>
@@ -83881,10 +83881,10 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="15" t="s">
         <v>1461</v>
       </c>
-      <c r="B20" s="16"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="7">
         <v>7.0400000000000004E-2</v>
       </c>
@@ -83896,10 +83896,10 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="15" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="16"/>
+      <c r="B21" s="15"/>
       <c r="C21">
         <v>3.2629999999999999</v>
       </c>
@@ -83911,10 +83911,10 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="15" t="s">
         <v>1462</v>
       </c>
-      <c r="B22" s="16"/>
+      <c r="B22" s="15"/>
       <c r="C22" t="s">
         <v>1463</v>
       </c>
@@ -83926,11 +83926,11 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="15" t="s">
         <v>1464</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
       <c r="G23" s="1">
         <v>0</v>
       </c>
@@ -83942,10 +83942,10 @@
       <c r="A24" s="13" t="s">
         <v>1465</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>1466</v>
       </c>
-      <c r="C24" s="16"/>
+      <c r="C24" s="15"/>
       <c r="G24" s="1">
         <v>0</v>
       </c>
@@ -83957,10 +83957,10 @@
       <c r="A25" s="12" t="s">
         <v>1467</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>1468</v>
       </c>
-      <c r="C25" s="16"/>
+      <c r="C25" s="15"/>
       <c r="G25" s="1">
         <v>0</v>
       </c>

--- a/analysis/experiment_analysis.xlsx
+++ b/analysis/experiment_analysis.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd10f741228aacd2/Desktop/cap pro kpi part 2/ajaysingh_2511011_part2_kpi_experiment/analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd10f741228aacd2/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{4C0E890B-C1A0-48F9-8170-5316E933612B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0894B88-696A-4720-AA8F-2BDE7443EF19}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{4C0E890B-C1A0-48F9-8170-5316E933612B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921723EE-F9EF-44A1-8569-2029303D321A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E1D1647-9F6C-4433-9AA0-21691AC0572E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3E1D1647-9F6C-4433-9AA0-21691AC0572E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Clean_data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Hypo &amp; AB test" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Clean_data!$A$1:$R$1401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$1401</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4505,7 +4505,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4553,12 +4553,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -4593,7 +4587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4614,9 +4608,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -83547,20 +83538,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>1447</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="15"/>
       <c r="G1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>723</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="17" t="s">
         <v>1469</v>
       </c>
-      <c r="L1" s="14"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="9" t="s">
@@ -83593,12 +83584,12 @@
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="16" t="s">
         <v>1448</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickBot="1">
       <c r="A4" t="s">
@@ -83846,10 +83837,10 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.6">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>1459</v>
       </c>
-      <c r="B17" s="18"/>
+      <c r="B17" s="17"/>
       <c r="G17" s="1">
         <v>0</v>
       </c>
@@ -83866,10 +83857,10 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>1460</v>
       </c>
-      <c r="B19" s="15"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="7">
         <v>3.1899999999999998E-2</v>
       </c>
@@ -83881,10 +83872,10 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>1461</v>
       </c>
-      <c r="B20" s="15"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="7">
         <v>7.0400000000000004E-2</v>
       </c>
@@ -83896,10 +83887,10 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="15"/>
+      <c r="B21" s="14"/>
       <c r="C21">
         <v>3.2629999999999999</v>
       </c>
@@ -83911,10 +83902,10 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>1462</v>
       </c>
-      <c r="B22" s="15"/>
+      <c r="B22" s="14"/>
       <c r="C22" t="s">
         <v>1463</v>
       </c>
@@ -83926,11 +83917,11 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>1464</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
       <c r="G23" s="1">
         <v>0</v>
       </c>
@@ -83942,10 +83933,10 @@
       <c r="A24" s="13" t="s">
         <v>1465</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>1466</v>
       </c>
-      <c r="C24" s="15"/>
+      <c r="C24" s="14"/>
       <c r="G24" s="1">
         <v>0</v>
       </c>
@@ -83957,10 +83948,10 @@
       <c r="A25" s="12" t="s">
         <v>1467</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>1468</v>
       </c>
-      <c r="C25" s="15"/>
+      <c r="C25" s="14"/>
       <c r="G25" s="1">
         <v>0</v>
       </c>
@@ -89399,16 +89390,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
